--- a/education_forms/042_poetic_devices_knowledge_quiz--education_forms.xlsx
+++ b/education_forms/042_poetic_devices_knowledge_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Poetic devices</t>
+          <t>What is the purpose of a metaphor?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>A comparison between two things</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Symbolism</t>
+          <t>What is a way of expressing an idea or concept through the use of symbols or images?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A way of using symbols, images, or objects to represent abstract ideas or concepts</t>
+          <t>An image or representation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alliteration</t>
+          <t>What is the effect of alliteration?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A way of using words that start with the same sound</t>
+          <t>Repeating sounds in a sentence or phrase</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Imagery</t>
+          <t>What is a way of making a comparison using the words 'like' or 'as'?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A way of using words to create a mental image of a person, place, or object</t>
+          <t>Using 'like' or 'as' to compare two things</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allusion</t>
+          <t>What is the effect of personification?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A reference to a person, place, or event in a text, especially in the Bible</t>
+          <t>Giving human-like qualities to non-human things</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Simile</t>
+          <t>What is a word that imitates the sound of what is being described?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A comparison of two things using 'like'</t>
+          <t>A word that imitates a sound</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hyperbole</t>
+          <t>What is the effect of allusion?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Exaggeration</t>
+          <t>Reference to a person, place, or event</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Personification</t>
+          <t>What is a repeated phrase or word?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Giving human-like qualities to objects or abstract ideas</t>
+          <t>A phrase or word that repeats</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Onomatopoeia</t>
+          <t>Ninth Question</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A word that imitates the sound of what is being described</t>
+          <t>Ninth Option</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Enjambment</t>
+          <t>What is a reference to a person, place, or event in the past?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The continuation of a sentence or phrase into the next line without a pause</t>
+          <t>A reference to the past</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Anaphora</t>
+          <t>Eleventh Question</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A repeated phrase or word at the beginning of successive clauses or lines</t>
+          <t>A repeated word</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Repetition</t>
+          <t>What is a mental image or picture?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>The repetition of a word or phrase</t>
+          <t>A mental picture</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Imagery</t>
+          <t>What is a comparison of two things using 'like' or 'as'?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>An image that creates a mental picture</t>
+          <t>A comparison using 'like' or 'as'</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Allusion</t>
+          <t>What is a repeated phrase or word at the beginning of successive clauses or lines?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>A reference to a person, place, or event</t>
+          <t>A repeated phrase or word</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Symbolism</t>
+          <t>What is a way of giving human-like qualities to objects or abstract ideas?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>A way of using symbols to represent abstract ideas or concepts</t>
+          <t>Giving human qualities to non-human things</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Imagery</t>
+          <t>Sixteenth Question</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1238,425 +1238,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>A way of creating a mental image</t>
+          <t>Sixteenth Option</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>seventeenth_question</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Hyperbole</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>seventeenth_option</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>An overstatement</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>eighteenth_question</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Metaphor</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>eighteenth_option</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>A comparison between two things without using ‘like’</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>nineteenth_question</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Juxtaposition</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>nineteenth_option</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Placing two images side by side to show their relationship</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>twentieth_question</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Allegory</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>twentieth_option</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>A story that uses a real event or person to represent a general truth</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>twentyfirst_question</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Personification</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>twentyfirst_option</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>A figure of speech that gives human-like qualities to objects or abstract things</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>twentysecond_question</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Imagery</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>twentysecond_option</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>A way of expressing an idea using mental images</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>twentythird_question</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Enjambment</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>twentythird_option</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>The continuation of a sentence or phrase into the next line without a pause</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>twentyfourth_question</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Anaphora</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>twentyfourth_option</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>A repeated word or phrase at the beginning of successive clauses</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>twentyfifth_question</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Repetition</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>twentyfifth_option</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>A repeated phrase or word</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1673,10 +1259,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1706,12 +1292,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option':_'a_figure_of_speech_that_makes_a_comparison_between__two_different_things'}</t>
+          <t>a_way_of_comparing_two_things</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option': 'A figure of speech that makes a comparison between  two different things'}</t>
+          <t>A way of comparing two things</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1309,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option':_'a_way_of_expressing_a_concept_or_idea'}</t>
+          <t>a_way_of_expressing_one_thing_as_another</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option': 'a way of expressing a concept or idea'}</t>
+          <t>A way of expressing one thing as another</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1326,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'an_image,_picture,_or_object_that_represents_an_idea_or_feeling'}</t>
+          <t>a_way_of_representing_an_idea_or_concept</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'An image, picture, or object that represents an idea or feeling'}</t>
+          <t>A way of representing an idea or concept</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1343,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'a_way_of_using_words_or_images_to_convey_meaning'}</t>
+          <t>a_way_of_conveying_meaning_through_images_or_symbols</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'A way of using words or images to convey meaning'}</t>
+          <t>A way of conveying meaning through images or symbols</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1360,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'words_that_are_pronounced_the_same'}</t>
+          <t>a_way_of_repeating_sounds</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'Words that are pronounced the same'}</t>
+          <t>A way of repeating sounds</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1377,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'words_that_start_with_the_same_sound'}</t>
+          <t>a_repetition_of_sounds</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'Words that start with the same sound'}</t>
+          <t>A repetition of sounds</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1394,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'a_description_of_the_senses'}</t>
+          <t>a_comparison_between_two_things</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'A description of the senses'}</t>
+          <t>A comparison between two things</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1411,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'a_way_of_creating_a_picture_in_the_mind'}</t>
+          <t>a_comparison_using_'like'_or_'as'</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'A way of creating a picture in the mind'}</t>
+          <t>A comparison using 'like' or 'as'</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1428,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'a_word_or_phrase_that_refers_to_a_thing_or_event_in_the_past'}</t>
+          <t>attributing_human_qualities_to_objects_or_concepts</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': 'A word or phrase that refers to a thing or event in the past'}</t>
+          <t>Attributing human qualities to objects or concepts</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1445,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'a_reference_to_something_in_the_bible_or_another_religious_text'}</t>
+          <t>giving_human_qualities_to_non-human_things</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': 'A reference to something in the Bible or another religious text'}</t>
+          <t>Giving human qualities to non-human things</t>
         </is>
       </c>
     </row>
@@ -1876,12 +1462,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'a_comparison_of_two_things_using_‘like’'}</t>
+          <t>a_word_that_imitates_the_sound</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': 'A comparison of two things using ‘like’'}</t>
+          <t>A word that imitates the sound</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1479,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'a_comparison_between_two_things'}</t>
+          <t>a_word_that_repeats_a_sound</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': 'A comparison between two things'}</t>
+          <t>A word that repeats a sound</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1496,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'an_overstatement'}</t>
+          <t>a_reference_to_the_past</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': 'An overstatement'}</t>
+          <t>A reference to the past</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1513,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'a_way_of_expressing_an_idea_that_is_stronger_than_the_reality'}</t>
+          <t>a_hint_of_something_in_the_past</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'A way of expressing an idea that is stronger than the reality'}</t>
+          <t>A hint of something in the past</t>
         </is>
       </c>
     </row>
@@ -1944,12 +1530,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'attributing_human_qualities_or_characteristics_to_non-human_things'}</t>
+          <t>a_repeated_phrase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'Attributing human qualities or characteristics to non-human things'}</t>
+          <t>A repeated phrase</t>
         </is>
       </c>
     </row>
@@ -1961,12 +1547,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'an_idea_or_object_that_is_given_human-like_qualities'}</t>
+          <t>a_repeated_word</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'An idea or object that is given human-like qualities'}</t>
+          <t>A repeated word</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1564,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option':_'a_word_that_imitates_the_sound'}</t>
+          <t>a_word_that_imitates_the_sound</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option': 'A word that imitates the sound'}</t>
+          <t>A word that imitates the sound</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1581,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option':_'a_word_that_imitates_the_sound_of_something'}</t>
+          <t>a_word_that_repeats_a_sound</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option': 'A word that imitates the sound of something'}</t>
+          <t>A word that repeats a sound</t>
         </is>
       </c>
     </row>
@@ -2012,12 +1598,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'option':_'a_sentence_or_phrase_that_continues_into_the_next_line'}</t>
+          <t>a_reference_to_something_in_the_past</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'option': 'A sentence or phrase that continues into the next line'}</t>
+          <t>A reference to something in the past</t>
         </is>
       </c>
     </row>
@@ -2029,12 +1615,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'option':_'continuation_of_a_sentence_or_phrase_without_a_pause'}</t>
+          <t>a_hint_of_something_in_the_past</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'option': 'Continuation of a sentence or phrase without a pause'}</t>
+          <t>A hint of something in the past</t>
         </is>
       </c>
     </row>
@@ -2046,12 +1632,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'option':_'a_repeated_phrase_or_word_at_the_beginning_of_successive_lines'}</t>
+          <t>a_repeated_word</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'option': 'A repeated phrase or word at the beginning of successive lines'}</t>
+          <t>A repeated word</t>
         </is>
       </c>
     </row>
@@ -2063,12 +1649,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'option':_'a_repeated_word_or_phrase_at_the_beginning_of_successive_clauses'}</t>
+          <t>a_repeated_phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'option': 'A repeated word or phrase at the beginning of successive clauses'}</t>
+          <t>A repeated phrase</t>
         </is>
       </c>
     </row>
@@ -2080,12 +1666,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'option':_'a_repeated_word_or_phrase'}</t>
+          <t>a_mental_image</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'option': 'A repeated word or phrase'}</t>
+          <t>A mental image</t>
         </is>
       </c>
     </row>
@@ -2097,12 +1683,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'option':_'repeating_a_word_or_phrase'}</t>
+          <t>a_mental_picture</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'option': 'Repeating a word or phrase'}</t>
+          <t>A mental picture</t>
         </is>
       </c>
     </row>
@@ -2114,12 +1700,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'option':_'a_picture_that_is_created_in_the_mind'}</t>
+          <t>a_comparison_using_'like'_or_'as'</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'option': 'A picture that is created in the mind'}</t>
+          <t>A comparison using 'like' or 'as'</t>
         </is>
       </c>
     </row>
@@ -2131,12 +1717,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'option':_'a_mental_picture'}</t>
+          <t>a_comparison_between_two_things</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'option': 'A mental picture'}</t>
+          <t>A comparison between two things</t>
         </is>
       </c>
     </row>
@@ -2148,12 +1734,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option':_'a_reference_to_a_person,_place,_or_event_in_the_past'}</t>
+          <t>a_repeated_phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option': 'A reference to a person, place, or event in the past'}</t>
+          <t>A repeated phrase</t>
         </is>
       </c>
     </row>
@@ -2165,12 +1751,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option':_'a_hint_of_something_in_the_past'}</t>
+          <t>a_repeated_word</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option': 'A hint of something in the past'}</t>
+          <t>A repeated word</t>
         </is>
       </c>
     </row>
@@ -2182,12 +1768,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option':_'a_representation_of_abstract_ideas_or_concepts'}</t>
+          <t>attributing_human_qualities_to_objects_or_concepts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option': 'A representation of abstract ideas or concepts'}</t>
+          <t>Attributing human qualities to objects or concepts</t>
         </is>
       </c>
     </row>
@@ -2199,12 +1785,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option':_'a_way_of_using_symbols'}</t>
+          <t>giving_human_qualities_to_non-human_things</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option': 'A way of using symbols'}</t>
+          <t>Giving human qualities to non-human things</t>
         </is>
       </c>
     </row>
@@ -2216,12 +1802,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option':_'a_description_that_creates_a_mental_picture'}</t>
+          <t>a_word_that_imitates_the_sound</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option': 'A description that creates a mental picture'}</t>
+          <t>A word that imitates the sound</t>
         </is>
       </c>
     </row>
@@ -2233,318 +1819,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option':_'a_way_of_creating_mental_images'}</t>
+          <t>a_word_that_repeats_a_sound</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option': 'A way of creating mental images'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>seventeenth_option_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'option':_'exaggeration'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'option': 'Exaggeration'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>seventeenth_option_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'option':_'saying_more_than_what_is_true'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'option': 'Saying more than what is true'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>eighteenth_option_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'option':_'a_comparison_without_‘like’'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'option': 'A comparison without ‘like’'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>eighteenth_option_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'option':_'a_comparison_between_two_things'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'option': 'A comparison between two things'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>nineteenth_option_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'option':_'side_by_side_comparison'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'option': 'Side by side comparison'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>nineteenth_option_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'option':_'placing_two_things_next_to_each_other'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'option': 'Placing two things next to each other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>twentieth_option_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'option':_'a_story_that_represents_a_general_truth'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'option': 'A story that represents a general truth'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>twentieth_option_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'option':_'an_extended_metaphor'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'option': 'An extended metaphor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>twentyfirst_option_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'option':_'giving_human_qualities_to_things_that_are_not_human'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'option': 'Giving human qualities to things that are not human'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>twentyfirst_option_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'option':_'attributing_human_qualities_to_objects_or_ideas'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'option': 'Attributing human qualities to objects or ideas'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>twentysecond_option_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'option':_'a_description_that_creates_a_mental_picture'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'option': 'A description that creates a mental picture'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>twentysecond_option_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'option':_'a_way_to_express_an_idea'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'option': 'A way to express an idea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>twentythird_option_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'option':_'a_sentence_that_continues_into_the_next_line'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'option': 'A sentence that continues into the next line'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>twentythird_option_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'option':_'continuation_of_a_sentence_into_the_next_line'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'option': 'Continuation of a sentence into the next line'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>twentyfourth_option_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'option':_'repeated_word_or_phrase_at_the_beginning'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'option': 'Repeated word or phrase at the beginning'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>twentyfourth_option_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'option':_'repeating_a_word_or_phrase'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'option': 'Repeating a word or phrase'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>twentyfifth_option_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'option':_'a_repeated_phrase_or_word'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'option': 'A repeated phrase or word'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>twentyfifth_option_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'option':_'repeating_a_phrase_or_word'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'option': 'Repeating a phrase or word'}</t>
+          <t>A word that repeats a sound</t>
         </is>
       </c>
     </row>
